--- a/apps/api/assets/vocabulary/初中/沪教版/沪教版牛津英语九年级下册.xlsx
+++ b/apps/api/assets/vocabulary/初中/沪教版/沪教版牛津英语九年级下册.xlsx
@@ -440,7 +440,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D196"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -1031,6 +1031,16 @@
           <t>open up</t>
         </is>
       </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. (打)开；割开；开发(资源)；揭示
@@ -1044,6 +1054,16 @@
           <t>go on a trip</t>
         </is>
       </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 去旅行；进行旅行；去旅游</t>
@@ -1079,6 +1099,16 @@
           <t>set sail</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 张帆；开船
@@ -1092,6 +1122,16 @@
           <t>known as</t>
         </is>
       </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 被称为；被认为是；以…而闻名</t>
@@ -1104,6 +1144,16 @@
           <t>be known as</t>
         </is>
       </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 通称
@@ -1140,6 +1190,16 @@
           <t>lead to</t>
         </is>
       </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 通向
@@ -1153,6 +1213,16 @@
           <t>compare ... with ...</t>
         </is>
       </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 和…比较[对照]
@@ -1164,6 +1234,16 @@
       <c r="A35" s="2" t="inlineStr">
         <is>
           <t>culture shock</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1782,6 +1862,16 @@
           <t>in one's spare time</t>
         </is>
       </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -1794,6 +1884,16 @@
           <t>to a certain degree</t>
         </is>
       </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 在某种程度上；到某种程度；相当
@@ -1807,6 +1907,16 @@
           <t>get used to</t>
         </is>
       </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 变得习惯于
@@ -1818,6 +1928,16 @@
       <c r="A65" s="2" t="inlineStr">
         <is>
           <t>under the weather</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -2395,6 +2515,16 @@
           <t>role model</t>
         </is>
       </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 楷模；榜样；典范
@@ -2408,6 +2538,16 @@
           <t>greenhouse effect</t>
         </is>
       </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 温室效应
@@ -2421,6 +2561,16 @@
           <t>in danger</t>
         </is>
       </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 在危险中
@@ -2434,6 +2584,16 @@
           <t>as a result of</t>
         </is>
       </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. (作)为…的结果
@@ -2447,6 +2607,16 @@
           <t>result in</t>
         </is>
       </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 终于(失败)
@@ -2460,6 +2630,16 @@
           <t>mountains of</t>
         </is>
       </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 大量的；许多</t>
@@ -2472,6 +2652,16 @@
           <t>take action</t>
         </is>
       </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 动手；采取行动；采取(快速)措施；提起诉讼
@@ -2483,6 +2673,16 @@
       <c r="A97" s="2" t="inlineStr">
         <is>
           <t>make a difference</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -3046,6 +3246,16 @@
           <t>natural disaster</t>
         </is>
       </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 灾难
@@ -3082,6 +3292,16 @@
           <t>stick with</t>
         </is>
       </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 坚持；继续支持；坚持做</t>
@@ -3094,6 +3314,16 @@
           <t>sit around</t>
         </is>
       </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 无所事事；坐着没事干；闲坐</t>
@@ -3106,6 +3336,16 @@
           <t>have no time to do</t>
         </is>
       </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -3118,6 +3358,16 @@
           <t>fall on deaf ears</t>
         </is>
       </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 不被理睬
@@ -3131,6 +3381,16 @@
           <t>stare at</t>
         </is>
       </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 瞪着看
@@ -3144,6 +3404,16 @@
           <t>in surprise</t>
         </is>
       </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">adv. 惊奇地
@@ -3157,6 +3427,16 @@
           <t>for now</t>
         </is>
       </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 眼下
@@ -3168,6 +3448,16 @@
       <c r="A130" s="2" t="inlineStr">
         <is>
           <t>survival kit</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -3700,6 +3990,16 @@
           <t>dying to</t>
         </is>
       </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 渴望；港人渴望；迫切</t>
@@ -3712,6 +4012,16 @@
           <t>be dying to</t>
         </is>
       </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 渴望；渴望，巴不得立即；非常渴望</t>
@@ -3724,6 +4034,16 @@
           <t>be dying to do sth.</t>
         </is>
       </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 渴望做某事；非常想做某事；急切去做</t>
@@ -3782,6 +4102,16 @@
           <t>can't wait to</t>
         </is>
       </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -3794,6 +4124,16 @@
           <t>can't wait to do sth.</t>
         </is>
       </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -3806,6 +4146,16 @@
           <t>to be honest</t>
         </is>
       </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 老实说；说实话；说实在的</t>
@@ -3818,6 +4168,16 @@
           <t>fall over</t>
         </is>
       </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 倒了；落在地上；(计算机)程序停止运行；跌倒
@@ -3829,6 +4189,16 @@
       <c r="A162" s="2" t="inlineStr">
         <is>
           <t>keep one's balance</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
@@ -4439,6 +4809,16 @@
           <t>deal with</t>
         </is>
       </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 办理；对待；与…交涉；与…交易
@@ -4452,6 +4832,16 @@
           <t>guard against</t>
         </is>
       </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 防止；加以预防；抵御
@@ -4465,6 +4855,16 @@
           <t>cancel out</t>
         </is>
       </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 相约；相消；抵消
@@ -4478,6 +4878,16 @@
           <t>look on the bright side</t>
         </is>
       </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 看光明的一面；你得看到事情好的一面；看到事物光明的一面</t>
@@ -4513,6 +4923,16 @@
           <t>busy with</t>
         </is>
       </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 忙于；忙着
@@ -4526,6 +4946,16 @@
           <t>be busy with</t>
         </is>
       </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 忙于
@@ -4539,6 +4969,16 @@
           <t>leave ... behind</t>
         </is>
       </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 遗留；留下；追过；留在后头
@@ -4550,6 +4990,16 @@
       <c r="A196" s="2" t="inlineStr">
         <is>
           <t>cheer ... up</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
